--- a/src/salary-data/drivers-results.xlsx
+++ b/src/salary-data/drivers-results.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -2597,12 +2597,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="0" t="n">
         <v>19</v>
       </c>
       <c r="C38" s="31" t="n">
@@ -2636,6 +2636,132 @@
       </c>
       <c r="N38" s="31" t="n">
         <v>11557</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>1509</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>274316</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>232262</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>7054</v>
+      </c>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>7054</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>1509</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>274316</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>232262</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>7054</v>
+      </c>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="n"/>
+      <c r="M40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>7054</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>19</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>1509</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>274316</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>232262</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="n">
+        <v>7054</v>
+      </c>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>7054</v>
       </c>
     </row>
   </sheetData>
@@ -2656,7 +2782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -4259,12 +4385,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="0" t="n">
         <v>22</v>
       </c>
       <c r="C31" s="31" t="n">
@@ -4302,6 +4428,144 @@
       </c>
       <c r="N31" s="31" t="n">
         <v>30054</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C32" s="31" t="n">
+        <v>1479</v>
+      </c>
+      <c r="D32" s="31" t="n">
+        <v>369120</v>
+      </c>
+      <c r="E32" s="31" t="n">
+        <v>309416</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>42:45</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="n">
+        <v>23485</v>
+      </c>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="M32" s="31" t="n">
+        <v>1219</v>
+      </c>
+      <c r="N32" s="31" t="n">
+        <v>24704</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C33" s="31" t="n">
+        <v>1479</v>
+      </c>
+      <c r="D33" s="31" t="n">
+        <v>369120</v>
+      </c>
+      <c r="E33" s="31" t="n">
+        <v>309416</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>42:45</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="n">
+        <v>23485</v>
+      </c>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="M33" s="31" t="n">
+        <v>1219</v>
+      </c>
+      <c r="N33" s="31" t="n">
+        <v>24704</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>21</v>
+      </c>
+      <c r="C34" s="31" t="n">
+        <v>1479</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>369120</v>
+      </c>
+      <c r="E34" s="31" t="n">
+        <v>309416</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>42:45</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="n">
+        <v>23485</v>
+      </c>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="M34" s="31" t="n">
+        <v>1219</v>
+      </c>
+      <c r="N34" s="31" t="n">
+        <v>24704</v>
       </c>
     </row>
   </sheetData>
@@ -4322,7 +4586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -5798,12 +6062,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="0" t="n">
         <v>23</v>
       </c>
       <c r="C29" s="31" t="n">
@@ -5841,6 +6105,96 @@
       </c>
       <c r="N29" s="31" t="n">
         <v>33141</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="10" t="n"/>
+      <c r="M30" s="31" t="n"/>
+      <c r="N30" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="31" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="31" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="31" t="n"/>
+      <c r="L31" s="10" t="n"/>
+      <c r="M31" s="31" t="n"/>
+      <c r="N31" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="31" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="31" t="n"/>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="31" t="n"/>
+      <c r="N32" s="31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7411,7 +7765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -9273,12 +9627,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="0" t="n">
         <v>21</v>
       </c>
       <c r="C36" s="31" t="n">
@@ -9316,6 +9670,144 @@
       </c>
       <c r="N36" s="31" t="n">
         <v>31464</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>1627</v>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>408726</v>
+      </c>
+      <c r="E37" s="31" t="n">
+        <v>340156</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>43:51</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="n">
+        <v>25712</v>
+      </c>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="M37" s="31" t="n">
+        <v>7858</v>
+      </c>
+      <c r="N37" s="31" t="n">
+        <v>33570</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <v>1627</v>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>408726</v>
+      </c>
+      <c r="E38" s="31" t="n">
+        <v>340156</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>43:51</t>
+        </is>
+      </c>
+      <c r="G38" s="31" t="n">
+        <v>25712</v>
+      </c>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="M38" s="31" t="n">
+        <v>7858</v>
+      </c>
+      <c r="N38" s="31" t="n">
+        <v>33570</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>22</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>1627</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>408726</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>340156</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>43:51</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>25712</v>
+      </c>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="M39" s="31" t="n">
+        <v>7858</v>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>33570</v>
       </c>
     </row>
   </sheetData>
@@ -9336,7 +9828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -11258,12 +11750,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="0" t="n">
         <v>24</v>
       </c>
       <c r="C36" s="31" t="n">
@@ -11305,6 +11797,144 @@
       </c>
       <c r="N36" s="31" t="n">
         <v>41433</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>1637</v>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>410005</v>
+      </c>
+      <c r="E37" s="31" t="n">
+        <v>342656</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>52:40</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="n">
+        <v>31013</v>
+      </c>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>27:59</t>
+        </is>
+      </c>
+      <c r="M37" s="31" t="n">
+        <v>1336</v>
+      </c>
+      <c r="N37" s="31" t="n">
+        <v>32349</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <v>1637</v>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>410005</v>
+      </c>
+      <c r="E38" s="31" t="n">
+        <v>342656</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>52:40</t>
+        </is>
+      </c>
+      <c r="G38" s="31" t="n">
+        <v>31013</v>
+      </c>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>27:59</t>
+        </is>
+      </c>
+      <c r="M38" s="31" t="n">
+        <v>1336</v>
+      </c>
+      <c r="N38" s="31" t="n">
+        <v>32349</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>21</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>1637</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>410005</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>342656</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>52:40</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>31013</v>
+      </c>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>27:59</t>
+        </is>
+      </c>
+      <c r="M39" s="31" t="n">
+        <v>1336</v>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>32349</v>
       </c>
     </row>
   </sheetData>
@@ -11325,7 +11955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -13260,12 +13890,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="0" t="n">
         <v>21</v>
       </c>
       <c r="C36" s="31" t="n">
@@ -13307,6 +13937,144 @@
       </c>
       <c r="N36" s="31" t="n">
         <v>46153</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>1723</v>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>410728</v>
+      </c>
+      <c r="E37" s="31" t="n">
+        <v>341526</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>43:01</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="n">
+        <v>27801</v>
+      </c>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>24:48</t>
+        </is>
+      </c>
+      <c r="M37" s="31" t="n">
+        <v>1401</v>
+      </c>
+      <c r="N37" s="31" t="n">
+        <v>29202</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <v>1723</v>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>410728</v>
+      </c>
+      <c r="E38" s="31" t="n">
+        <v>341526</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>43:01</t>
+        </is>
+      </c>
+      <c r="G38" s="31" t="n">
+        <v>27801</v>
+      </c>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>24:48</t>
+        </is>
+      </c>
+      <c r="M38" s="31" t="n">
+        <v>1401</v>
+      </c>
+      <c r="N38" s="31" t="n">
+        <v>29202</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>20</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>1723</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>410728</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>341526</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>43:01</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>27801</v>
+      </c>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>24:48</t>
+        </is>
+      </c>
+      <c r="M39" s="31" t="n">
+        <v>1401</v>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>29202</v>
       </c>
     </row>
   </sheetData>
@@ -13327,7 +14095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -15339,12 +16107,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="0" t="n">
         <v>23</v>
       </c>
       <c r="C38" s="31" t="n">
@@ -15382,6 +16150,144 @@
       </c>
       <c r="N38" s="31" t="n">
         <v>33696</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>421156</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>365675</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>15772</v>
+      </c>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="M39" s="31" t="n">
+        <v>4709</v>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>20481</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>421156</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>365675</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>15772</v>
+      </c>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="M40" s="31" t="n">
+        <v>4709</v>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>20481</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>21</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>421156</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>365675</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="n">
+        <v>15772</v>
+      </c>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="M41" s="31" t="n">
+        <v>4709</v>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>20481</v>
       </c>
     </row>
   </sheetData>
@@ -15402,7 +16308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -17359,12 +18265,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="0" t="n">
         <v>22</v>
       </c>
       <c r="C38" s="31" t="n">
@@ -17398,6 +18304,96 @@
       </c>
       <c r="N38" s="31" t="n">
         <v>27180</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="31" t="n"/>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="31" t="n"/>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="31" t="n"/>
+      <c r="N39" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="31" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="31" t="n"/>
+      <c r="L40" s="10" t="n"/>
+      <c r="M40" s="31" t="n"/>
+      <c r="N40" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="31" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="31" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="31" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="31" t="n"/>
+      <c r="N41" s="31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -17418,7 +18414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -19451,12 +20447,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="0" t="n">
         <v>18</v>
       </c>
       <c r="C38" s="31" t="n">
@@ -19494,6 +20490,144 @@
       </c>
       <c r="N38" s="31" t="n">
         <v>30343</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>361813</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>292314</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>35:13</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>23068</v>
+      </c>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="M39" s="31" t="n">
+        <v>6431</v>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>29499</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>361813</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>292314</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>35:13</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>23068</v>
+      </c>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="M40" s="31" t="n">
+        <v>6431</v>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>29499</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>17</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>361813</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>292314</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>35:13</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="n">
+        <v>23068</v>
+      </c>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="M41" s="31" t="n">
+        <v>6431</v>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>29499</v>
       </c>
     </row>
   </sheetData>
@@ -20658,7 +21792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -22623,12 +23757,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>2025.04</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="0" t="n">
         <v>19</v>
       </c>
       <c r="C38" s="31" t="n">
@@ -22666,6 +23800,96 @@
       </c>
       <c r="N38" s="31" t="n">
         <v>8213</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="31" t="n"/>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="31" t="n"/>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="31" t="n"/>
+      <c r="N39" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="31" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="31" t="n"/>
+      <c r="L40" s="10" t="n"/>
+      <c r="M40" s="31" t="n"/>
+      <c r="N40" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="31" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="31" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="31" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="31" t="n"/>
+      <c r="N41" s="31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/salary-data/drivers-results.xlsx
+++ b/src/salary-data/drivers-results.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -2723,12 +2723,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>19</v>
       </c>
       <c r="C41" s="31" t="n">
@@ -2761,6 +2761,132 @@
         <v>0</v>
       </c>
       <c r="N41" s="31" t="n">
+        <v>7054</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <v>1509</v>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>274316</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>232262</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>7054</v>
+      </c>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="31" t="n">
+        <v>7054</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C43" s="31" t="n">
+        <v>1509</v>
+      </c>
+      <c r="D43" s="31" t="n">
+        <v>274316</v>
+      </c>
+      <c r="E43" s="31" t="n">
+        <v>232262</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G43" s="31" t="n">
+        <v>7054</v>
+      </c>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="10" t="n"/>
+      <c r="M43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="31" t="n">
+        <v>7054</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>19</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <v>1509</v>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>274316</v>
+      </c>
+      <c r="E44" s="31" t="n">
+        <v>232262</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G44" s="31" t="n">
+        <v>7054</v>
+      </c>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="31" t="n">
         <v>7054</v>
       </c>
     </row>
@@ -2782,7 +2908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -4523,12 +4649,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="0" t="n">
         <v>21</v>
       </c>
       <c r="C34" s="31" t="n">
@@ -4565,6 +4691,144 @@
         <v>1219</v>
       </c>
       <c r="N34" s="31" t="n">
+        <v>24704</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C35" s="31" t="n">
+        <v>1479</v>
+      </c>
+      <c r="D35" s="31" t="n">
+        <v>369120</v>
+      </c>
+      <c r="E35" s="31" t="n">
+        <v>309416</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>42:45</t>
+        </is>
+      </c>
+      <c r="G35" s="31" t="n">
+        <v>23485</v>
+      </c>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="M35" s="31" t="n">
+        <v>1219</v>
+      </c>
+      <c r="N35" s="31" t="n">
+        <v>24704</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C36" s="31" t="n">
+        <v>1479</v>
+      </c>
+      <c r="D36" s="31" t="n">
+        <v>369120</v>
+      </c>
+      <c r="E36" s="31" t="n">
+        <v>309416</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>42:45</t>
+        </is>
+      </c>
+      <c r="G36" s="31" t="n">
+        <v>23485</v>
+      </c>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="10" t="n"/>
+      <c r="K36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="M36" s="31" t="n">
+        <v>1219</v>
+      </c>
+      <c r="N36" s="31" t="n">
+        <v>24704</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>21</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>1479</v>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>369120</v>
+      </c>
+      <c r="E37" s="31" t="n">
+        <v>309416</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>42:45</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="n">
+        <v>23485</v>
+      </c>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>2:13</t>
+        </is>
+      </c>
+      <c r="M37" s="31" t="n">
+        <v>1219</v>
+      </c>
+      <c r="N37" s="31" t="n">
         <v>24704</v>
       </c>
     </row>
@@ -4586,7 +4850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -6168,12 +6432,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="31" t="n">
@@ -6194,6 +6458,96 @@
       <c r="L32" s="10" t="n"/>
       <c r="M32" s="31" t="n"/>
       <c r="N32" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="31" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="31" t="n"/>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="31" t="n"/>
+      <c r="L33" s="10" t="n"/>
+      <c r="M33" s="31" t="n"/>
+      <c r="N33" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="10" t="n"/>
+      <c r="M34" s="31" t="n"/>
+      <c r="N34" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="31" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="31" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="31" t="n"/>
+      <c r="L35" s="10" t="n"/>
+      <c r="M35" s="31" t="n"/>
+      <c r="N35" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7765,7 +8119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -9765,12 +10119,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="0" t="n">
         <v>22</v>
       </c>
       <c r="C39" s="31" t="n">
@@ -9807,6 +10161,144 @@
         <v>7858</v>
       </c>
       <c r="N39" s="31" t="n">
+        <v>33570</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>1627</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>408726</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>340156</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>43:51</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>25712</v>
+      </c>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="M40" s="31" t="n">
+        <v>7858</v>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>33570</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>1627</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>408726</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>340156</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>43:51</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="n">
+        <v>25712</v>
+      </c>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="M41" s="31" t="n">
+        <v>7858</v>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>33570</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>22</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <v>1627</v>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>408726</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>340156</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>43:51</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>25712</v>
+      </c>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="M42" s="31" t="n">
+        <v>7858</v>
+      </c>
+      <c r="N42" s="31" t="n">
         <v>33570</v>
       </c>
     </row>
@@ -9828,7 +10320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -11892,12 +12384,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="0" t="n">
         <v>21</v>
       </c>
       <c r="C39" s="31" t="n">
@@ -11934,6 +12426,144 @@
         <v>1336</v>
       </c>
       <c r="N39" s="31" t="n">
+        <v>32349</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>1637</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>410005</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>342656</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>52:40</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>31013</v>
+      </c>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>27:59</t>
+        </is>
+      </c>
+      <c r="M40" s="31" t="n">
+        <v>1336</v>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>32349</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>1637</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>410005</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>342656</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>52:40</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="n">
+        <v>31013</v>
+      </c>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>27:59</t>
+        </is>
+      </c>
+      <c r="M41" s="31" t="n">
+        <v>1336</v>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>32349</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>21</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <v>1637</v>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>410005</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>342656</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>52:40</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>31013</v>
+      </c>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>2:16</t>
+        </is>
+      </c>
+      <c r="M42" s="31" t="n">
+        <v>1336</v>
+      </c>
+      <c r="N42" s="31" t="n">
         <v>32349</v>
       </c>
     </row>
@@ -11955,7 +12585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -14032,12 +14662,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="0" t="n">
         <v>20</v>
       </c>
       <c r="C39" s="31" t="n">
@@ -14074,6 +14704,144 @@
         <v>1401</v>
       </c>
       <c r="N39" s="31" t="n">
+        <v>29202</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>1723</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>410728</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>341526</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>43:01</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>27801</v>
+      </c>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>24:48</t>
+        </is>
+      </c>
+      <c r="M40" s="31" t="n">
+        <v>1401</v>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>29202</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>1723</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>410728</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>341526</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>43:01</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="n">
+        <v>27801</v>
+      </c>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>24:48</t>
+        </is>
+      </c>
+      <c r="M41" s="31" t="n">
+        <v>1401</v>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>29202</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <v>1723</v>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>410728</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>341526</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>43:01</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>27801</v>
+      </c>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>2:10</t>
+        </is>
+      </c>
+      <c r="M42" s="31" t="n">
+        <v>1401</v>
+      </c>
+      <c r="N42" s="31" t="n">
         <v>29202</v>
       </c>
     </row>
@@ -14095,7 +14863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -16245,12 +17013,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>21</v>
       </c>
       <c r="C41" s="31" t="n">
@@ -16287,6 +17055,144 @@
         <v>4709</v>
       </c>
       <c r="N41" s="31" t="n">
+        <v>20481</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>421156</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>365675</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>15772</v>
+      </c>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="M42" s="31" t="n">
+        <v>4709</v>
+      </c>
+      <c r="N42" s="31" t="n">
+        <v>20481</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C43" s="31" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D43" s="31" t="n">
+        <v>421156</v>
+      </c>
+      <c r="E43" s="31" t="n">
+        <v>365675</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="G43" s="31" t="n">
+        <v>15772</v>
+      </c>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="M43" s="31" t="n">
+        <v>4709</v>
+      </c>
+      <c r="N43" s="31" t="n">
+        <v>20481</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>21</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>421156</v>
+      </c>
+      <c r="E44" s="31" t="n">
+        <v>365675</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="G44" s="31" t="n">
+        <v>15772</v>
+      </c>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>7:06</t>
+        </is>
+      </c>
+      <c r="M44" s="31" t="n">
+        <v>4709</v>
+      </c>
+      <c r="N44" s="31" t="n">
         <v>20481</v>
       </c>
     </row>
@@ -16308,7 +17214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -18367,12 +19273,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="31" t="n">
@@ -18393,6 +19299,96 @@
       <c r="L41" s="10" t="n"/>
       <c r="M41" s="31" t="n"/>
       <c r="N41" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="31" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="31" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="31" t="n"/>
+      <c r="N42" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="31" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="31" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="31" t="n"/>
+      <c r="L43" s="10" t="n"/>
+      <c r="M43" s="31" t="n"/>
+      <c r="N43" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="31" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="31" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="31" t="n"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="31" t="n"/>
+      <c r="N44" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18414,7 +19410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -20585,12 +21581,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>17</v>
       </c>
       <c r="C41" s="31" t="n">
@@ -20627,6 +21623,144 @@
         <v>6431</v>
       </c>
       <c r="N41" s="31" t="n">
+        <v>29499</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>361813</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>292314</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>35:13</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>23068</v>
+      </c>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="M42" s="31" t="n">
+        <v>6431</v>
+      </c>
+      <c r="N42" s="31" t="n">
+        <v>29499</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" s="31" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D43" s="31" t="n">
+        <v>361813</v>
+      </c>
+      <c r="E43" s="31" t="n">
+        <v>292314</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>35:13</t>
+        </is>
+      </c>
+      <c r="G43" s="31" t="n">
+        <v>23068</v>
+      </c>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="M43" s="31" t="n">
+        <v>6431</v>
+      </c>
+      <c r="N43" s="31" t="n">
+        <v>29499</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>17</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>361813</v>
+      </c>
+      <c r="E44" s="31" t="n">
+        <v>292314</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>35:13</t>
+        </is>
+      </c>
+      <c r="G44" s="31" t="n">
+        <v>23068</v>
+      </c>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>9:49</t>
+        </is>
+      </c>
+      <c r="M44" s="31" t="n">
+        <v>6431</v>
+      </c>
+      <c r="N44" s="31" t="n">
         <v>29499</v>
       </c>
     </row>
@@ -21792,7 +22926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
@@ -23863,12 +24997,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>2026.09</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="31" t="n">
@@ -23889,6 +25023,96 @@
       <c r="L41" s="10" t="n"/>
       <c r="M41" s="31" t="n"/>
       <c r="N41" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="31" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="31" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="31" t="n"/>
+      <c r="N42" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="31" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="31" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="31" t="n"/>
+      <c r="L43" s="10" t="n"/>
+      <c r="M43" s="31" t="n"/>
+      <c r="N43" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="31" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="31" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="31" t="n"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="31" t="n"/>
+      <c r="N44" s="31" t="n">
         <v>0</v>
       </c>
     </row>
